--- a/output/2026-10-16/enriched_analysis.xlsx
+++ b/output/2026-10-16/enriched_analysis.xlsx
@@ -1396,7 +1396,7 @@
         <v>0.021</v>
       </c>
       <c r="W4" t="n">
-        <v>3434</v>
+        <v>3436</v>
       </c>
       <c r="X4" t="n">
         <v>15.6</v>
@@ -1628,7 +1628,7 @@
         <v>0.045</v>
       </c>
       <c r="W5" t="n">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="X5" t="n">
         <v>10.1</v>
@@ -1857,13 +1857,13 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>1.041</v>
+        <v>1.044</v>
       </c>
       <c r="W6" t="n">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="X6" t="n">
-        <v>86.90000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="Y6" t="n">
         <v>111</v>
@@ -2089,13 +2089,13 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>1.103</v>
+        <v>1.14</v>
       </c>
       <c r="W7" t="n">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="X7" t="n">
-        <v>7.73</v>
+        <v>7.47</v>
       </c>
       <c r="Y7" t="n">
         <v>17</v>
@@ -2324,7 +2324,7 @@
         <v>0.048</v>
       </c>
       <c r="W8" t="n">
-        <v>14877</v>
+        <v>14891</v>
       </c>
       <c r="X8" t="n">
         <v>37.9</v>
@@ -2553,13 +2553,13 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>2.299</v>
+        <v>2.315</v>
       </c>
       <c r="W9" t="n">
-        <v>2553</v>
+        <v>2535</v>
       </c>
       <c r="X9" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Y9" t="n">
         <v>6</v>
@@ -2788,7 +2788,7 @@
         <v>0.052</v>
       </c>
       <c r="W10" t="n">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="X10" t="n">
         <v>21.2</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>0.47</v>
+        <v>0.469</v>
       </c>
       <c r="W12" t="n">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="X12" t="n">
         <v>15.4</v>
@@ -3481,13 +3481,13 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>0.123</v>
+        <v>0.126</v>
       </c>
       <c r="W13" t="n">
-        <v>706</v>
+        <v>689</v>
       </c>
       <c r="X13" t="n">
-        <v>26.6</v>
+        <v>26</v>
       </c>
       <c r="Y13" t="n">
         <v>13</v>
@@ -3716,10 +3716,10 @@
         <v>0.127</v>
       </c>
       <c r="W14" t="n">
-        <v>2477</v>
+        <v>2469</v>
       </c>
       <c r="X14" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="Y14" t="n">
         <v>-3</v>
@@ -3948,10 +3948,10 @@
         <v>0.064</v>
       </c>
       <c r="W15" t="n">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="X15" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="Y15" t="n">
         <v>19</v>
@@ -4408,7 +4408,7 @@
         <v>0.178</v>
       </c>
       <c r="W17" t="n">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="X17" t="n">
         <v>39.3</v>
@@ -4640,10 +4640,10 @@
         <v>0.057</v>
       </c>
       <c r="W18" t="n">
-        <v>2236</v>
+        <v>2225</v>
       </c>
       <c r="X18" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Y18" t="n">
         <v>13</v>
@@ -4869,13 +4869,13 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>1.239</v>
+        <v>1.231</v>
       </c>
       <c r="W19" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="X19" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Y19" t="n">
         <v>22</v>
@@ -5104,10 +5104,10 @@
         <v>0.241</v>
       </c>
       <c r="W20" t="n">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="X20" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="Y20" t="n">
         <v>8</v>
@@ -5331,13 +5331,13 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>0.161</v>
+        <v>0.162</v>
       </c>
       <c r="W21" t="n">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="X21" t="n">
-        <v>57.5</v>
+        <v>57</v>
       </c>
       <c r="Y21" t="n">
         <v>3</v>
@@ -5563,13 +5563,13 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>1.509</v>
+        <v>1.513</v>
       </c>
       <c r="W22" t="n">
-        <v>8970</v>
+        <v>8944</v>
       </c>
       <c r="X22" t="n">
-        <v>1510</v>
+        <v>1506</v>
       </c>
       <c r="Y22" t="n">
         <v>-53</v>
@@ -5795,10 +5795,10 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>1.785</v>
+        <v>1.799</v>
       </c>
       <c r="W23" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="n">
@@ -6028,10 +6028,10 @@
         <v>0.068</v>
       </c>
       <c r="W24" t="n">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="X24" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="Y24" t="n">
         <v>20</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>3.169</v>
+        <v>3.179</v>
       </c>
       <c r="W25" t="n">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="X25" t="n">
         <v>18.7</v>
@@ -6483,13 +6483,13 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.577</v>
+        <v>0.579</v>
       </c>
       <c r="W26" t="n">
-        <v>2474</v>
+        <v>2468</v>
       </c>
       <c r="X26" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="Y26" t="n">
         <v>8</v>
@@ -6718,7 +6718,7 @@
         <v>0.103</v>
       </c>
       <c r="W27" t="n">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="X27" t="n">
         <v>36.3</v>
@@ -6941,13 +6941,13 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>0.319</v>
+        <v>0.318</v>
       </c>
       <c r="W28" t="n">
-        <v>59591</v>
+        <v>59742</v>
       </c>
       <c r="X28" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="Y28" t="n">
         <v>5</v>
@@ -7173,13 +7173,13 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>0.548</v>
+        <v>0.549</v>
       </c>
       <c r="W29" t="n">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="X29" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="Y29" t="n">
         <v>13</v>
@@ -7405,13 +7405,13 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>0.339</v>
+        <v>0.341</v>
       </c>
       <c r="W30" t="n">
-        <v>954</v>
+        <v>948</v>
       </c>
       <c r="X30" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="Y30" t="n">
         <v>13</v>
@@ -7640,7 +7640,7 @@
         <v>0.148</v>
       </c>
       <c r="W31" t="n">
-        <v>1423</v>
+        <v>1426</v>
       </c>
       <c r="X31" t="n">
         <v>14.2</v>
@@ -8101,13 +8101,13 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>0.093</v>
+        <v>0.091</v>
       </c>
       <c r="W33" t="n">
-        <v>613</v>
+        <v>624</v>
       </c>
       <c r="X33" t="n">
-        <v>9.98</v>
+        <v>10.2</v>
       </c>
       <c r="Y33" t="n">
         <v>-5</v>
@@ -8336,10 +8336,10 @@
         <v>0.121</v>
       </c>
       <c r="W34" t="n">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="X34" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="Y34" t="n">
         <v>-1</v>
@@ -8565,13 +8565,13 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>1.671</v>
+        <v>1.633</v>
       </c>
       <c r="W35" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="X35" t="n">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="Y35" t="n">
         <v>-14</v>
@@ -8803,7 +8803,7 @@
         <v>176</v>
       </c>
       <c r="X36" t="n">
-        <v>5.14</v>
+        <v>5.16</v>
       </c>
       <c r="Y36" t="n">
         <v>31</v>
@@ -9025,13 +9025,13 @@
         </is>
       </c>
       <c r="V37" t="n">
-        <v>1.136</v>
+        <v>1.135</v>
       </c>
       <c r="W37" t="n">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="X37" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Y37" t="n">
         <v>12</v>
@@ -9260,10 +9260,10 @@
         <v>0.174</v>
       </c>
       <c r="W38" t="n">
-        <v>3678</v>
+        <v>3669</v>
       </c>
       <c r="X38" t="n">
-        <v>6.93</v>
+        <v>6.91</v>
       </c>
       <c r="Y38" t="n">
         <v>2</v>
@@ -9455,7 +9455,7 @@
         <v>-4</v>
       </c>
       <c r="L39" t="n">
-        <v>75</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="M39" t="n">
         <v>4.84</v>
@@ -9492,7 +9492,7 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W39" t="n">
-        <v>54802</v>
+        <v>54808</v>
       </c>
       <c r="X39" t="n">
         <v>46.4</v>
@@ -9724,7 +9724,7 @@
         <v>0.01</v>
       </c>
       <c r="W40" t="n">
-        <v>15211</v>
+        <v>15205</v>
       </c>
       <c r="X40" t="n">
         <v>14</v>
@@ -9955,7 +9955,7 @@
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="n">
-        <v>5.96</v>
+        <v>5.97</v>
       </c>
       <c r="Y41" t="n">
         <v>-68</v>
@@ -10184,7 +10184,7 @@
         <v>0.004</v>
       </c>
       <c r="W42" t="n">
-        <v>45053</v>
+        <v>45157</v>
       </c>
       <c r="X42" t="n">
         <v>334</v>
@@ -10413,13 +10413,13 @@
         </is>
       </c>
       <c r="V43" t="n">
-        <v>0.372</v>
+        <v>0.374</v>
       </c>
       <c r="W43" t="n">
-        <v>1059</v>
+        <v>1052</v>
       </c>
       <c r="X43" t="n">
-        <v>53.9</v>
+        <v>53.6</v>
       </c>
       <c r="Y43" t="n">
         <v>21</v>
@@ -10645,13 +10645,13 @@
         </is>
       </c>
       <c r="V44" t="n">
-        <v>0.529</v>
+        <v>0.525</v>
       </c>
       <c r="W44" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="X44" t="n">
-        <v>35</v>
+        <v>35.2</v>
       </c>
       <c r="Y44" t="n">
         <v>21</v>
@@ -10880,7 +10880,7 @@
         <v>0.045</v>
       </c>
       <c r="W45" t="n">
-        <v>5170</v>
+        <v>5172</v>
       </c>
       <c r="X45" t="n">
         <v>26.9</v>
@@ -11344,10 +11344,10 @@
         <v>0.043</v>
       </c>
       <c r="W47" t="n">
-        <v>1607</v>
+        <v>1614</v>
       </c>
       <c r="X47" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="Y47" t="n">
         <v>10</v>
@@ -11579,7 +11579,7 @@
         <v>210</v>
       </c>
       <c r="X48" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="Y48" t="n">
         <v>-44</v>
@@ -11808,10 +11808,10 @@
         <v>0.272</v>
       </c>
       <c r="W49" t="n">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="X49" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="Y49" t="n">
         <v>9</v>
@@ -12037,10 +12037,10 @@
         </is>
       </c>
       <c r="V50" t="n">
-        <v>4.583</v>
+        <v>4.601</v>
       </c>
       <c r="W50" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="n">
@@ -12273,7 +12273,7 @@
         <v>349</v>
       </c>
       <c r="X51" t="n">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="Y51" t="n">
         <v>-61</v>
@@ -12721,13 +12721,13 @@
         </is>
       </c>
       <c r="V53" t="n">
-        <v>0.361</v>
+        <v>0.362</v>
       </c>
       <c r="W53" t="n">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="X53" t="n">
-        <v>96</v>
+        <v>95.8</v>
       </c>
       <c r="Y53" t="n">
         <v>246</v>
@@ -12953,10 +12953,10 @@
         </is>
       </c>
       <c r="V54" t="n">
-        <v>0.238</v>
+        <v>0.237</v>
       </c>
       <c r="W54" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="X54" t="n">
         <v>14.4</v>
@@ -13188,10 +13188,10 @@
         <v>0.029</v>
       </c>
       <c r="W55" t="n">
-        <v>7395</v>
+        <v>7412</v>
       </c>
       <c r="X55" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="Y55" t="n">
         <v>25</v>
@@ -13413,10 +13413,10 @@
         </is>
       </c>
       <c r="V56" t="n">
-        <v>0.84</v>
+        <v>0.841</v>
       </c>
       <c r="W56" t="n">
-        <v>3761</v>
+        <v>3758</v>
       </c>
       <c r="X56" t="n">
         <v>26.3</v>
@@ -13645,13 +13645,13 @@
         </is>
       </c>
       <c r="V57" t="n">
-        <v>0.232</v>
+        <v>0.231</v>
       </c>
       <c r="W57" t="n">
-        <v>1722</v>
+        <v>1727</v>
       </c>
       <c r="X57" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="Y57" t="n">
         <v>-3</v>
@@ -13877,13 +13877,13 @@
         </is>
       </c>
       <c r="V58" t="n">
-        <v>0.247</v>
+        <v>0.246</v>
       </c>
       <c r="W58" t="n">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="X58" t="n">
-        <v>53</v>
+        <v>53.1</v>
       </c>
       <c r="Y58" t="n">
         <v>-4</v>
@@ -14109,13 +14109,13 @@
         </is>
       </c>
       <c r="V59" t="n">
-        <v>0.184</v>
+        <v>0.186</v>
       </c>
       <c r="W59" t="n">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="X59" t="n">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="Y59" t="n">
         <v>-1</v>
@@ -14573,13 +14573,13 @@
         </is>
       </c>
       <c r="V61" t="n">
-        <v>0.264</v>
+        <v>0.263</v>
       </c>
       <c r="W61" t="n">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="X61" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Y61" t="n">
         <v>-66</v>
@@ -14808,7 +14808,7 @@
         <v>0.04</v>
       </c>
       <c r="W62" t="n">
-        <v>3338</v>
+        <v>3335</v>
       </c>
       <c r="X62" t="n">
         <v>19.8</v>
@@ -15269,13 +15269,13 @@
         </is>
       </c>
       <c r="V64" t="n">
-        <v>0.106</v>
+        <v>0.105</v>
       </c>
       <c r="W64" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="X64" t="n">
-        <v>7.58</v>
+        <v>7.62</v>
       </c>
       <c r="Y64" t="n">
         <v>118</v>
@@ -15729,10 +15729,10 @@
         </is>
       </c>
       <c r="V66" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="W66" t="n">
-        <v>3885</v>
+        <v>3944</v>
       </c>
       <c r="X66" t="inlineStr"/>
       <c r="Y66" t="n">
@@ -15962,10 +15962,10 @@
         <v>0.076</v>
       </c>
       <c r="W67" t="n">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="X67" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="Y67" t="n">
         <v>-8</v>
@@ -16194,7 +16194,7 @@
         <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>4937</v>
+        <v>4952</v>
       </c>
       <c r="X68" t="n">
         <v>11.6</v>
@@ -16658,10 +16658,10 @@
         <v>0.033</v>
       </c>
       <c r="W70" t="n">
-        <v>1472</v>
+        <v>1469</v>
       </c>
       <c r="X70" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="Y70" t="n">
         <v>11</v>
@@ -16890,7 +16890,7 @@
         <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>3347</v>
+        <v>3348</v>
       </c>
       <c r="X71" t="n">
         <v>43.6</v>
@@ -17122,7 +17122,7 @@
         <v>0.003</v>
       </c>
       <c r="W72" t="n">
-        <v>12731</v>
+        <v>12734</v>
       </c>
       <c r="X72" t="n">
         <v>40.6</v>
@@ -17354,10 +17354,10 @@
         <v>0.031</v>
       </c>
       <c r="W73" t="n">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="X73" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="Y73" t="n">
         <v>27</v>
@@ -17586,7 +17586,7 @@
         <v>0.052</v>
       </c>
       <c r="W74" t="n">
-        <v>957</v>
+        <v>949</v>
       </c>
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="n">
@@ -17816,10 +17816,10 @@
         <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>3812</v>
+        <v>3805</v>
       </c>
       <c r="X75" t="n">
-        <v>85.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="Y75" t="n">
         <v>42</v>
@@ -18048,10 +18048,10 @@
         <v>0.006</v>
       </c>
       <c r="W76" t="n">
-        <v>4828</v>
+        <v>4825</v>
       </c>
       <c r="X76" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="Y76" t="n">
         <v>23</v>
@@ -18276,7 +18276,7 @@
         <v>0</v>
       </c>
       <c r="W77" t="n">
-        <v>30214</v>
+        <v>30198</v>
       </c>
       <c r="X77" t="n">
         <v>226</v>
@@ -18508,10 +18508,10 @@
         <v>0</v>
       </c>
       <c r="W78" t="n">
-        <v>104998</v>
+        <v>105069</v>
       </c>
       <c r="X78" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="Y78" t="n">
         <v>18</v>
@@ -18967,13 +18967,13 @@
         </is>
       </c>
       <c r="V80" t="n">
-        <v>0.234</v>
+        <v>0.231</v>
       </c>
       <c r="W80" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="X80" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="Y80" t="n">
         <v>21</v>
@@ -19202,7 +19202,7 @@
         <v>0.026</v>
       </c>
       <c r="W81" t="n">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="X81" t="n">
         <v>37.3</v>
@@ -19419,10 +19419,10 @@
         </is>
       </c>
       <c r="V82" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="W82" t="n">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="n">
@@ -20962,7 +20962,7 @@
         <v>-4</v>
       </c>
       <c r="F39" t="n">
-        <v>75</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="G39" t="n">
         <v>4.84</v>

--- a/output/2026-10-16/enriched_analysis.xlsx
+++ b/output/2026-10-16/enriched_analysis.xlsx
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="W2" t="n">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="X2" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Y2" t="n">
         <v>47</v>
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>2.334</v>
+        <v>2.316</v>
       </c>
       <c r="W3" t="n">
-        <v>2700</v>
+        <v>2721</v>
       </c>
       <c r="X3" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="Y3" t="n">
         <v>75</v>
@@ -1396,10 +1396,10 @@
         <v>0.021</v>
       </c>
       <c r="W4" t="n">
-        <v>3436</v>
+        <v>3486</v>
       </c>
       <c r="X4" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="Y4" t="n">
         <v>18</v>
@@ -1628,10 +1628,10 @@
         <v>0.045</v>
       </c>
       <c r="W5" t="n">
-        <v>2928</v>
+        <v>2924</v>
       </c>
       <c r="X5" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="Y5" t="n">
         <v>36</v>
@@ -1857,13 +1857,13 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>1.044</v>
+        <v>1.05</v>
       </c>
       <c r="W6" t="n">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="X6" t="n">
-        <v>86.5</v>
+        <v>86</v>
       </c>
       <c r="Y6" t="n">
         <v>111</v>
@@ -2089,13 +2089,13 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>1.14</v>
+        <v>1.167</v>
       </c>
       <c r="W7" t="n">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="X7" t="n">
-        <v>7.47</v>
+        <v>7.33</v>
       </c>
       <c r="Y7" t="n">
         <v>17</v>
@@ -2321,13 +2321,13 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>0.048</v>
+        <v>0.045</v>
       </c>
       <c r="W8" t="n">
-        <v>14891</v>
+        <v>16118</v>
       </c>
       <c r="X8" t="n">
-        <v>37.9</v>
+        <v>41</v>
       </c>
       <c r="Y8" t="n">
         <v>83</v>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>2.315</v>
+        <v>2.309</v>
       </c>
       <c r="W9" t="n">
-        <v>2535</v>
+        <v>2542</v>
       </c>
       <c r="X9" t="n">
         <v>199</v>
@@ -2785,13 +2785,13 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="W10" t="n">
-        <v>1572</v>
+        <v>1622</v>
       </c>
       <c r="X10" t="n">
-        <v>21.2</v>
+        <v>21.8</v>
       </c>
       <c r="Y10" t="n">
         <v>55</v>
@@ -3017,13 +3017,13 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>0.338</v>
+        <v>0.337</v>
       </c>
       <c r="W11" t="n">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="X11" t="n">
-        <v>8.92</v>
+        <v>8.94</v>
       </c>
       <c r="Y11" t="n">
         <v>7</v>
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="V12" t="n">
-        <v>0.469</v>
+        <v>0.465</v>
       </c>
       <c r="W12" t="n">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="X12" t="n">
-        <v>15.4</v>
+        <v>15.6</v>
       </c>
       <c r="Y12" t="n">
         <v>19</v>
@@ -3481,13 +3481,13 @@
         </is>
       </c>
       <c r="V13" t="n">
-        <v>0.126</v>
+        <v>0.125</v>
       </c>
       <c r="W13" t="n">
-        <v>689</v>
+        <v>698</v>
       </c>
       <c r="X13" t="n">
-        <v>26</v>
+        <v>26.4</v>
       </c>
       <c r="Y13" t="n">
         <v>13</v>
@@ -3713,13 +3713,13 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>0.127</v>
+        <v>0.123</v>
       </c>
       <c r="W14" t="n">
-        <v>2469</v>
+        <v>2558</v>
       </c>
       <c r="X14" t="n">
-        <v>21.6</v>
+        <v>22.4</v>
       </c>
       <c r="Y14" t="n">
         <v>-3</v>
@@ -3945,13 +3945,13 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>0.064</v>
+        <v>0.062</v>
       </c>
       <c r="W15" t="n">
-        <v>889</v>
+        <v>909</v>
       </c>
       <c r="X15" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="Y15" t="n">
         <v>19</v>
@@ -4175,10 +4175,10 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>1.966</v>
+        <v>1.901</v>
       </c>
       <c r="W16" t="n">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="n">
@@ -4405,13 +4405,13 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>0.178</v>
+        <v>0.179</v>
       </c>
       <c r="W17" t="n">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="X17" t="n">
-        <v>39.3</v>
+        <v>39.1</v>
       </c>
       <c r="Y17" t="n">
         <v>2</v>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="V18" t="n">
-        <v>0.057</v>
+        <v>0.056</v>
       </c>
       <c r="W18" t="n">
-        <v>2225</v>
+        <v>2252</v>
       </c>
       <c r="X18" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Y18" t="n">
         <v>13</v>
@@ -4869,13 +4869,13 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>1.231</v>
+        <v>1.207</v>
       </c>
       <c r="W19" t="n">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="X19" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="Y19" t="n">
         <v>22</v>
@@ -5101,13 +5101,13 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.241</v>
+        <v>0.231</v>
       </c>
       <c r="W20" t="n">
-        <v>1426</v>
+        <v>1492</v>
       </c>
       <c r="X20" t="n">
-        <v>24.2</v>
+        <v>25.4</v>
       </c>
       <c r="Y20" t="n">
         <v>8</v>
@@ -5331,13 +5331,13 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>0.162</v>
+        <v>0.174</v>
       </c>
       <c r="W21" t="n">
-        <v>682</v>
+        <v>635</v>
       </c>
       <c r="X21" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="Y21" t="n">
         <v>3</v>
@@ -5563,13 +5563,13 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>1.513</v>
+        <v>1.493</v>
       </c>
       <c r="W22" t="n">
-        <v>8944</v>
+        <v>9065</v>
       </c>
       <c r="X22" t="n">
-        <v>1506</v>
+        <v>1526</v>
       </c>
       <c r="Y22" t="n">
         <v>-53</v>
@@ -5795,10 +5795,10 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>1.799</v>
+        <v>1.77</v>
       </c>
       <c r="W23" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="n">
@@ -6025,13 +6025,13 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>0.068</v>
+        <v>0.067</v>
       </c>
       <c r="W24" t="n">
-        <v>1639</v>
+        <v>1648</v>
       </c>
       <c r="X24" t="n">
-        <v>37.6</v>
+        <v>37.8</v>
       </c>
       <c r="Y24" t="n">
         <v>20</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>3.179</v>
+        <v>3.184</v>
       </c>
       <c r="W25" t="n">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="X25" t="n">
         <v>18.7</v>
@@ -6483,13 +6483,13 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.579</v>
+        <v>0.57</v>
       </c>
       <c r="W26" t="n">
-        <v>2468</v>
+        <v>2504</v>
       </c>
       <c r="X26" t="n">
-        <v>20.2</v>
+        <v>20.5</v>
       </c>
       <c r="Y26" t="n">
         <v>8</v>
@@ -6715,13 +6715,13 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>0.103</v>
+        <v>0.105</v>
       </c>
       <c r="W27" t="n">
-        <v>833</v>
+        <v>817</v>
       </c>
       <c r="X27" t="n">
-        <v>36.3</v>
+        <v>35.6</v>
       </c>
       <c r="Y27" t="n">
         <v>17</v>
@@ -6941,13 +6941,13 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>0.318</v>
+        <v>0.312</v>
       </c>
       <c r="W28" t="n">
-        <v>59742</v>
+        <v>60937</v>
       </c>
       <c r="X28" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="Y28" t="n">
         <v>5</v>
@@ -7173,13 +7173,13 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>0.549</v>
+        <v>0.542</v>
       </c>
       <c r="W29" t="n">
-        <v>901</v>
+        <v>912</v>
       </c>
       <c r="X29" t="n">
-        <v>15.9</v>
+        <v>16.1</v>
       </c>
       <c r="Y29" t="n">
         <v>13</v>
@@ -7405,13 +7405,13 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>0.341</v>
+        <v>0.342</v>
       </c>
       <c r="W30" t="n">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="X30" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="Y30" t="n">
         <v>13</v>
@@ -7637,13 +7637,13 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>0.148</v>
+        <v>0.145</v>
       </c>
       <c r="W31" t="n">
-        <v>1426</v>
+        <v>1458</v>
       </c>
       <c r="X31" t="n">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="Y31" t="n">
         <v>152</v>
@@ -7869,13 +7869,13 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="W32" t="n">
-        <v>1724</v>
+        <v>1853</v>
       </c>
       <c r="X32" t="n">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="Y32" t="n">
         <v>-48</v>
@@ -8101,13 +8101,13 @@
         </is>
       </c>
       <c r="V33" t="n">
-        <v>0.091</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="W33" t="n">
-        <v>624</v>
+        <v>655</v>
       </c>
       <c r="X33" t="n">
-        <v>10.2</v>
+        <v>10.7</v>
       </c>
       <c r="Y33" t="n">
         <v>-5</v>
@@ -8333,10 +8333,10 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>0.121</v>
+        <v>0.122</v>
       </c>
       <c r="W34" t="n">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="X34" t="n">
         <v>14.5</v>
@@ -8565,13 +8565,13 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>1.633</v>
+        <v>1.652</v>
       </c>
       <c r="W35" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="X35" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="Y35" t="n">
         <v>-14</v>
@@ -8797,13 +8797,13 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>1.127</v>
+        <v>1.14</v>
       </c>
       <c r="W36" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="X36" t="n">
-        <v>5.16</v>
+        <v>5.1</v>
       </c>
       <c r="Y36" t="n">
         <v>31</v>
@@ -9025,10 +9025,10 @@
         </is>
       </c>
       <c r="V37" t="n">
-        <v>1.135</v>
+        <v>1.131</v>
       </c>
       <c r="W37" t="n">
-        <v>1751</v>
+        <v>1757</v>
       </c>
       <c r="X37" t="n">
         <v>261</v>
@@ -9257,13 +9257,13 @@
         </is>
       </c>
       <c r="V38" t="n">
-        <v>0.174</v>
+        <v>0.173</v>
       </c>
       <c r="W38" t="n">
-        <v>3669</v>
+        <v>3689</v>
       </c>
       <c r="X38" t="n">
-        <v>6.91</v>
+        <v>6.95</v>
       </c>
       <c r="Y38" t="n">
         <v>2</v>
@@ -9492,10 +9492,10 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W39" t="n">
-        <v>54808</v>
+        <v>55263</v>
       </c>
       <c r="X39" t="n">
-        <v>46.4</v>
+        <v>46.8</v>
       </c>
       <c r="Y39" t="n">
         <v>5</v>
@@ -9724,7 +9724,7 @@
         <v>0.01</v>
       </c>
       <c r="W40" t="n">
-        <v>15205</v>
+        <v>15303</v>
       </c>
       <c r="X40" t="n">
         <v>14</v>
@@ -9955,7 +9955,7 @@
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="n">
-        <v>5.97</v>
+        <v>6.26</v>
       </c>
       <c r="Y41" t="n">
         <v>-68</v>
@@ -10184,10 +10184,10 @@
         <v>0.004</v>
       </c>
       <c r="W42" t="n">
-        <v>45157</v>
+        <v>44672</v>
       </c>
       <c r="X42" t="n">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="Y42" t="n">
         <v>26</v>
@@ -10413,13 +10413,13 @@
         </is>
       </c>
       <c r="V43" t="n">
-        <v>0.374</v>
+        <v>0.371</v>
       </c>
       <c r="W43" t="n">
-        <v>1052</v>
+        <v>1060</v>
       </c>
       <c r="X43" t="n">
-        <v>53.6</v>
+        <v>54</v>
       </c>
       <c r="Y43" t="n">
         <v>21</v>
@@ -10645,13 +10645,13 @@
         </is>
       </c>
       <c r="V44" t="n">
-        <v>0.525</v>
+        <v>0.532</v>
       </c>
       <c r="W44" t="n">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="X44" t="n">
-        <v>35.2</v>
+        <v>34.8</v>
       </c>
       <c r="Y44" t="n">
         <v>21</v>
@@ -10880,10 +10880,10 @@
         <v>0.045</v>
       </c>
       <c r="W45" t="n">
-        <v>5172</v>
+        <v>5218</v>
       </c>
       <c r="X45" t="n">
-        <v>26.9</v>
+        <v>27.1</v>
       </c>
       <c r="Y45" t="n">
         <v>13</v>
@@ -11109,13 +11109,13 @@
         </is>
       </c>
       <c r="V46" t="n">
-        <v>0.325</v>
+        <v>0.328</v>
       </c>
       <c r="W46" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="X46" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="Y46" t="n">
         <v>12</v>
@@ -11344,10 +11344,10 @@
         <v>0.043</v>
       </c>
       <c r="W47" t="n">
-        <v>1614</v>
+        <v>1602</v>
       </c>
       <c r="X47" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="Y47" t="n">
         <v>10</v>
@@ -11501,57 +11501,57 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AFFORDABLE</t>
+          <t>WCIL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
+          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C48" t="n">
+        <v>5</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
         <v>7</v>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>10</v>
-      </c>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H48" t="n">
         <v>-1</v>
       </c>
       <c r="I48" t="n">
-        <v>165.47</v>
+        <v>93.97</v>
       </c>
       <c r="J48" t="n">
-        <v>174.27</v>
+        <v>96.03</v>
       </c>
       <c r="K48" t="n">
-        <v>-5</v>
+        <v>-2.1</v>
       </c>
       <c r="L48" t="n">
-        <v>61.48</v>
+        <v>71.89</v>
       </c>
       <c r="M48" t="n">
-        <v>1.07</v>
+        <v>2.6</v>
       </c>
       <c r="N48" t="n">
-        <v>10743104</v>
+        <v>26023230</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>10743104</v>
+        <v>26023230</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -11565,60 +11565,60 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="V48" t="n">
-        <v>0.512</v>
+        <v>0.272</v>
       </c>
       <c r="W48" t="n">
-        <v>210</v>
+        <v>956</v>
       </c>
       <c r="X48" t="n">
-        <v>36.3</v>
+        <v>26</v>
       </c>
       <c r="Y48" t="n">
-        <v>-44</v>
+        <v>9</v>
       </c>
       <c r="Z48" t="n">
-        <v>-3.28</v>
+        <v>18.68</v>
       </c>
       <c r="AA48" t="n">
-        <v>141</v>
+        <v>-36</v>
       </c>
       <c r="AB48" t="n">
-        <v>-4.05</v>
+        <v>0.85</v>
       </c>
       <c r="AC48" t="n">
-        <v>8.67</v>
+        <v>6.83</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.44</v>
+        <v>0.26</v>
       </c>
       <c r="AE48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>-35.96</v>
+        <v>4.02</v>
       </c>
       <c r="AG48" t="n">
-        <v>169.48</v>
+        <v>89.68000000000001</v>
       </c>
       <c r="AH48" t="n">
-        <v>176.27</v>
+        <v>99.52</v>
       </c>
       <c r="AI48" t="n">
-        <v>-11.4</v>
+        <v>-5.1</v>
       </c>
       <c r="AJ48" t="n">
-        <v>174.2652478588113</v>
+        <v>96.02667896678967</v>
       </c>
       <c r="AK48" t="n">
-        <v>-5</v>
+        <v>-2.1</v>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
@@ -11637,22 +11637,22 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="AQ48" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AR48" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AS48" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AT48" t="n">
         <v>0</v>
@@ -11661,13 +11661,13 @@
         <v>0</v>
       </c>
       <c r="AV48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW48" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AX48" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AY48" t="n">
         <v>0</v>
@@ -11676,13 +11676,13 @@
         <v>0</v>
       </c>
       <c r="BA48" t="n">
-        <v>9361398</v>
+        <v>26023230</v>
       </c>
       <c r="BB48" t="n">
-        <v>10743104</v>
+        <v>26023230</v>
       </c>
       <c r="BC48" t="n">
-        <v>10743104</v>
+        <v>26023230</v>
       </c>
       <c r="BD48" t="n">
         <v>0</v>
@@ -11718,7 +11718,7 @@
         <v>0</v>
       </c>
       <c r="BO48" t="n">
-        <v>9361398</v>
+        <v>26023230</v>
       </c>
       <c r="BP48" t="n">
         <v>1</v>
@@ -11733,12 +11733,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>WCIL</t>
+          <t>AFFORDABLE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
+          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -11750,40 +11750,40 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
         <v>-1</v>
       </c>
       <c r="I49" t="n">
-        <v>93.97</v>
+        <v>165.47</v>
       </c>
       <c r="J49" t="n">
-        <v>96.03</v>
+        <v>174.27</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.1</v>
+        <v>-5</v>
       </c>
       <c r="L49" t="n">
-        <v>71.89</v>
+        <v>61.48</v>
       </c>
       <c r="M49" t="n">
-        <v>2.6</v>
+        <v>1.07</v>
       </c>
       <c r="N49" t="n">
-        <v>26023230</v>
+        <v>10743104</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>26023230</v>
+        <v>10743104</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -11797,60 +11797,60 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="V49" t="n">
-        <v>0.272</v>
+        <v>0.5</v>
       </c>
       <c r="W49" t="n">
-        <v>958</v>
+        <v>215</v>
       </c>
       <c r="X49" t="n">
-        <v>26.1</v>
+        <v>37.2</v>
       </c>
       <c r="Y49" t="n">
-        <v>9</v>
+        <v>-44</v>
       </c>
       <c r="Z49" t="n">
-        <v>18.68</v>
+        <v>-3.28</v>
       </c>
       <c r="AA49" t="n">
-        <v>-36</v>
+        <v>141</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.85</v>
+        <v>-4.05</v>
       </c>
       <c r="AC49" t="n">
-        <v>6.83</v>
+        <v>8.67</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.26</v>
+        <v>0.44</v>
       </c>
       <c r="AE49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF49" t="n">
-        <v>4.02</v>
+        <v>-35.96</v>
       </c>
       <c r="AG49" t="n">
-        <v>89.68000000000001</v>
+        <v>169.48</v>
       </c>
       <c r="AH49" t="n">
-        <v>99.52</v>
+        <v>176.27</v>
       </c>
       <c r="AI49" t="n">
-        <v>-5.1</v>
+        <v>-11.4</v>
       </c>
       <c r="AJ49" t="n">
-        <v>96.02667896678967</v>
+        <v>174.2652478588113</v>
       </c>
       <c r="AK49" t="n">
-        <v>-2.1</v>
+        <v>-5</v>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
@@ -11869,22 +11869,22 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AQ49" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AR49" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AS49" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AT49" t="n">
         <v>0</v>
@@ -11893,13 +11893,13 @@
         <v>0</v>
       </c>
       <c r="AV49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW49" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AX49" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY49" t="n">
         <v>0</v>
@@ -11908,13 +11908,13 @@
         <v>0</v>
       </c>
       <c r="BA49" t="n">
-        <v>26023230</v>
+        <v>9361398</v>
       </c>
       <c r="BB49" t="n">
-        <v>26023230</v>
+        <v>10743104</v>
       </c>
       <c r="BC49" t="n">
-        <v>26023230</v>
+        <v>10743104</v>
       </c>
       <c r="BD49" t="n">
         <v>0</v>
@@ -11950,7 +11950,7 @@
         <v>0</v>
       </c>
       <c r="BO49" t="n">
-        <v>26023230</v>
+        <v>9361398</v>
       </c>
       <c r="BP49" t="n">
         <v>1</v>
@@ -12037,10 +12037,10 @@
         </is>
       </c>
       <c r="V50" t="n">
-        <v>4.601</v>
+        <v>4.509</v>
       </c>
       <c r="W50" t="n">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="n">
@@ -12267,13 +12267,13 @@
         </is>
       </c>
       <c r="V51" t="n">
-        <v>0.673</v>
+        <v>0.65</v>
       </c>
       <c r="W51" t="n">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="X51" t="n">
-        <v>1127</v>
+        <v>1164</v>
       </c>
       <c r="Y51" t="n">
         <v>-61</v>
@@ -12721,13 +12721,13 @@
         </is>
       </c>
       <c r="V53" t="n">
-        <v>0.362</v>
+        <v>0.365</v>
       </c>
       <c r="W53" t="n">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="X53" t="n">
-        <v>95.8</v>
+        <v>95</v>
       </c>
       <c r="Y53" t="n">
         <v>246</v>
@@ -12953,13 +12953,13 @@
         </is>
       </c>
       <c r="V54" t="n">
-        <v>0.237</v>
+        <v>0.239</v>
       </c>
       <c r="W54" t="n">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="X54" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="Y54" t="n">
         <v>16</v>
@@ -13188,10 +13188,10 @@
         <v>0.029</v>
       </c>
       <c r="W55" t="n">
-        <v>7412</v>
+        <v>7363</v>
       </c>
       <c r="X55" t="n">
-        <v>29.7</v>
+        <v>29.5</v>
       </c>
       <c r="Y55" t="n">
         <v>25</v>
@@ -13413,10 +13413,10 @@
         </is>
       </c>
       <c r="V56" t="n">
-        <v>0.841</v>
+        <v>0.843</v>
       </c>
       <c r="W56" t="n">
-        <v>3758</v>
+        <v>3749</v>
       </c>
       <c r="X56" t="n">
         <v>26.3</v>
@@ -13648,7 +13648,7 @@
         <v>0.231</v>
       </c>
       <c r="W57" t="n">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="X57" t="n">
         <v>18.3</v>
@@ -13877,13 +13877,13 @@
         </is>
       </c>
       <c r="V58" t="n">
-        <v>0.246</v>
+        <v>0.25</v>
       </c>
       <c r="W58" t="n">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="X58" t="n">
-        <v>53.1</v>
+        <v>52.3</v>
       </c>
       <c r="Y58" t="n">
         <v>-4</v>
@@ -14109,13 +14109,13 @@
         </is>
       </c>
       <c r="V59" t="n">
-        <v>0.186</v>
+        <v>0.187</v>
       </c>
       <c r="W59" t="n">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="X59" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="Y59" t="n">
         <v>-1</v>
@@ -14341,13 +14341,13 @@
         </is>
       </c>
       <c r="V60" t="n">
-        <v>0.479</v>
+        <v>0.474</v>
       </c>
       <c r="W60" t="n">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="X60" t="n">
-        <v>41.9</v>
+        <v>42.4</v>
       </c>
       <c r="Y60" t="n">
         <v>6</v>
@@ -14573,13 +14573,13 @@
         </is>
       </c>
       <c r="V61" t="n">
-        <v>0.263</v>
+        <v>0.266</v>
       </c>
       <c r="W61" t="n">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="X61" t="n">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="Y61" t="n">
         <v>-66</v>
@@ -14805,13 +14805,13 @@
         </is>
       </c>
       <c r="V62" t="n">
-        <v>0.04</v>
+        <v>0.041</v>
       </c>
       <c r="W62" t="n">
-        <v>3335</v>
+        <v>3287</v>
       </c>
       <c r="X62" t="n">
-        <v>19.8</v>
+        <v>19.5</v>
       </c>
       <c r="Y62" t="n">
         <v>-4</v>
@@ -15037,13 +15037,13 @@
         </is>
       </c>
       <c r="V63" t="n">
-        <v>0.306</v>
+        <v>0.311</v>
       </c>
       <c r="W63" t="n">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="X63" t="n">
-        <v>62.7</v>
+        <v>61.7</v>
       </c>
       <c r="Y63" t="n">
         <v>13</v>
@@ -15269,13 +15269,13 @@
         </is>
       </c>
       <c r="V64" t="n">
-        <v>0.105</v>
+        <v>0.103</v>
       </c>
       <c r="W64" t="n">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="X64" t="n">
-        <v>7.62</v>
+        <v>7.78</v>
       </c>
       <c r="Y64" t="n">
         <v>118</v>
@@ -15497,13 +15497,13 @@
         </is>
       </c>
       <c r="V65" t="n">
-        <v>0.147</v>
+        <v>0.15</v>
       </c>
       <c r="W65" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="X65" t="n">
-        <v>31.7</v>
+        <v>31.3</v>
       </c>
       <c r="Y65" t="n">
         <v>19</v>
@@ -15732,7 +15732,7 @@
         <v>0.011</v>
       </c>
       <c r="W66" t="n">
-        <v>3944</v>
+        <v>3906</v>
       </c>
       <c r="X66" t="inlineStr"/>
       <c r="Y66" t="n">
@@ -15959,13 +15959,13 @@
         </is>
       </c>
       <c r="V67" t="n">
-        <v>0.076</v>
+        <v>0.074</v>
       </c>
       <c r="W67" t="n">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="X67" t="n">
-        <v>13</v>
+        <v>13.4</v>
       </c>
       <c r="Y67" t="n">
         <v>-8</v>
@@ -16194,7 +16194,7 @@
         <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>4952</v>
+        <v>4937</v>
       </c>
       <c r="X68" t="n">
         <v>11.6</v>
@@ -16423,13 +16423,13 @@
         </is>
       </c>
       <c r="V69" t="n">
-        <v>0.1</v>
+        <v>0.099</v>
       </c>
       <c r="W69" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="X69" t="n">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="Y69" t="n">
         <v>24</v>
@@ -16658,10 +16658,10 @@
         <v>0.033</v>
       </c>
       <c r="W70" t="n">
-        <v>1469</v>
+        <v>1478</v>
       </c>
       <c r="X70" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="Y70" t="n">
         <v>11</v>
@@ -16890,10 +16890,10 @@
         <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>3348</v>
+        <v>3405</v>
       </c>
       <c r="X71" t="n">
-        <v>43.6</v>
+        <v>44.3</v>
       </c>
       <c r="Y71" t="n">
         <v>5</v>
@@ -17122,7 +17122,7 @@
         <v>0.003</v>
       </c>
       <c r="W72" t="n">
-        <v>12734</v>
+        <v>12739</v>
       </c>
       <c r="X72" t="n">
         <v>40.6</v>
@@ -17354,10 +17354,10 @@
         <v>0.031</v>
       </c>
       <c r="W73" t="n">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="X73" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="Y73" t="n">
         <v>27</v>
@@ -17583,10 +17583,10 @@
         </is>
       </c>
       <c r="V74" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="W74" t="n">
-        <v>949</v>
+        <v>964</v>
       </c>
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="n">
@@ -17816,10 +17816,10 @@
         <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>3805</v>
+        <v>3830</v>
       </c>
       <c r="X75" t="n">
-        <v>85.59999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="Y75" t="n">
         <v>42</v>
@@ -18048,7 +18048,7 @@
         <v>0.006</v>
       </c>
       <c r="W76" t="n">
-        <v>4825</v>
+        <v>4800</v>
       </c>
       <c r="X76" t="n">
         <v>12.4</v>
@@ -18276,10 +18276,10 @@
         <v>0</v>
       </c>
       <c r="W77" t="n">
-        <v>30198</v>
+        <v>30977</v>
       </c>
       <c r="X77" t="n">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="Y77" t="n">
         <v>62</v>
@@ -18508,10 +18508,10 @@
         <v>0</v>
       </c>
       <c r="W78" t="n">
-        <v>105069</v>
+        <v>107211</v>
       </c>
       <c r="X78" t="n">
-        <v>30.3</v>
+        <v>30.9</v>
       </c>
       <c r="Y78" t="n">
         <v>18</v>
@@ -18737,10 +18737,10 @@
         </is>
       </c>
       <c r="V79" t="n">
-        <v>0.358</v>
+        <v>0.355</v>
       </c>
       <c r="W79" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="n">
@@ -18967,13 +18967,13 @@
         </is>
       </c>
       <c r="V80" t="n">
-        <v>0.231</v>
+        <v>0.239</v>
       </c>
       <c r="W80" t="n">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="X80" t="n">
-        <v>23.1</v>
+        <v>22.3</v>
       </c>
       <c r="Y80" t="n">
         <v>21</v>
@@ -19199,13 +19199,13 @@
         </is>
       </c>
       <c r="V81" t="n">
-        <v>0.026</v>
+        <v>0.025</v>
       </c>
       <c r="W81" t="n">
-        <v>1535</v>
+        <v>1581</v>
       </c>
       <c r="X81" t="n">
-        <v>37.3</v>
+        <v>38.4</v>
       </c>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="n">
@@ -19419,10 +19419,10 @@
         </is>
       </c>
       <c r="V82" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="W82" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="n">
@@ -21259,70 +21259,70 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AFFORDABLE</t>
+          <t>WCIL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
+          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>165.47</v>
+        <v>93.97</v>
       </c>
       <c r="D48" t="n">
-        <v>174.27</v>
+        <v>96.03</v>
       </c>
       <c r="E48" t="n">
-        <v>-5</v>
+        <v>-2.1</v>
       </c>
       <c r="F48" t="n">
-        <v>61.48</v>
+        <v>71.89</v>
       </c>
       <c r="G48" t="n">
-        <v>1.07</v>
+        <v>2.6</v>
       </c>
       <c r="H48" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>WCIL</t>
+          <t>AFFORDABLE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
+          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>93.97</v>
+        <v>165.47</v>
       </c>
       <c r="D49" t="n">
-        <v>96.03</v>
+        <v>174.27</v>
       </c>
       <c r="E49" t="n">
-        <v>-2.1</v>
+        <v>-5</v>
       </c>
       <c r="F49" t="n">
-        <v>71.89</v>
+        <v>61.48</v>
       </c>
       <c r="G49" t="n">
-        <v>2.6</v>
+        <v>1.07</v>
       </c>
       <c r="H49" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
     </row>

--- a/output/2026-10-16/enriched_analysis.xlsx
+++ b/output/2026-10-16/enriched_analysis.xlsx
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>2.327</v>
+        <v>2.325</v>
       </c>
       <c r="W3" t="n">
-        <v>2708</v>
+        <v>2710</v>
       </c>
       <c r="X3" t="n">
         <v>21.2</v>
@@ -1396,10 +1396,10 @@
         <v>0.021</v>
       </c>
       <c r="W4" t="n">
-        <v>3456</v>
+        <v>3453</v>
       </c>
       <c r="X4" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="Y4" t="n">
         <v>18</v>
@@ -1628,10 +1628,10 @@
         <v>0.046</v>
       </c>
       <c r="W5" t="n">
-        <v>2903</v>
+        <v>2906</v>
       </c>
       <c r="X5" t="n">
-        <v>9.98</v>
+        <v>9.99</v>
       </c>
       <c r="Y5" t="n">
         <v>36</v>
@@ -2317,13 +2317,13 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>1.072</v>
+        <v>1.075</v>
       </c>
       <c r="W8" t="n">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="X8" t="n">
-        <v>84.40000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="Y8" t="n">
         <v>111</v>
@@ -2555,7 +2555,7 @@
         <v>181</v>
       </c>
       <c r="X9" t="n">
-        <v>7.71</v>
+        <v>7.68</v>
       </c>
       <c r="Y9" t="n">
         <v>17</v>
@@ -2784,10 +2784,10 @@
         <v>0.045</v>
       </c>
       <c r="W10" t="n">
-        <v>15869</v>
+        <v>15839</v>
       </c>
       <c r="X10" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="Y10" t="n">
         <v>83</v>
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="V11" t="n">
-        <v>2.265</v>
+        <v>2.26</v>
       </c>
       <c r="W11" t="n">
-        <v>2591</v>
+        <v>2597</v>
       </c>
       <c r="X11" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Y11" t="n">
         <v>6</v>
@@ -3251,7 +3251,7 @@
         <v>933</v>
       </c>
       <c r="X12" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="Y12" t="n">
         <v>2</v>
@@ -3480,10 +3480,10 @@
         <v>0.052</v>
       </c>
       <c r="W13" t="n">
-        <v>1596</v>
+        <v>1584</v>
       </c>
       <c r="X13" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="Y13" t="n">
         <v>55</v>
@@ -3709,13 +3709,13 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>0.34</v>
+        <v>0.338</v>
       </c>
       <c r="W14" t="n">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="X14" t="n">
-        <v>8.859999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="Y14" t="n">
         <v>7</v>
@@ -3941,13 +3941,13 @@
         </is>
       </c>
       <c r="V15" t="n">
-        <v>0.468</v>
+        <v>0.469</v>
       </c>
       <c r="W15" t="n">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="X15" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="Y15" t="n">
         <v>19</v>
@@ -4173,13 +4173,13 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>0.124</v>
+        <v>0.125</v>
       </c>
       <c r="W16" t="n">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="X16" t="n">
-        <v>26.5</v>
+        <v>26.2</v>
       </c>
       <c r="Y16" t="n">
         <v>13</v>
@@ -4870,7 +4870,7 @@
         <v>0.056</v>
       </c>
       <c r="W19" t="n">
-        <v>2253</v>
+        <v>2262</v>
       </c>
       <c r="X19" t="n">
         <v>105</v>
@@ -5099,13 +5099,13 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>1.511</v>
+        <v>1.497</v>
       </c>
       <c r="W20" t="n">
-        <v>8954</v>
+        <v>9037</v>
       </c>
       <c r="X20" t="n">
-        <v>1507</v>
+        <v>1521</v>
       </c>
       <c r="Y20" t="n">
         <v>-53</v>
@@ -5331,13 +5331,13 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>1.219</v>
+        <v>1.243</v>
       </c>
       <c r="W21" t="n">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="X21" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="Y21" t="n">
         <v>22</v>
@@ -5563,13 +5563,13 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>0.571</v>
+        <v>0.572</v>
       </c>
       <c r="W22" t="n">
-        <v>2499</v>
+        <v>2496</v>
       </c>
       <c r="X22" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="Y22" t="n">
         <v>8</v>
@@ -5795,13 +5795,13 @@
         </is>
       </c>
       <c r="V23" t="n">
-        <v>0.314</v>
+        <v>0.313</v>
       </c>
       <c r="W23" t="n">
-        <v>60537</v>
+        <v>60748</v>
       </c>
       <c r="X23" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="Y23" t="n">
         <v>5</v>
@@ -6030,10 +6030,10 @@
         <v>0.068</v>
       </c>
       <c r="W24" t="n">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="X24" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="Y24" t="n">
         <v>20</v>
@@ -6259,10 +6259,10 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>3.094</v>
+        <v>3.089</v>
       </c>
       <c r="W25" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="X25" t="n">
         <v>19.2</v>
@@ -6485,13 +6485,13 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.18</v>
+        <v>0.177</v>
       </c>
       <c r="W26" t="n">
-        <v>616</v>
+        <v>626</v>
       </c>
       <c r="X26" t="n">
-        <v>51.4</v>
+        <v>52.3</v>
       </c>
       <c r="Y26" t="n">
         <v>3</v>
@@ -6717,13 +6717,13 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>0.106</v>
+        <v>0.107</v>
       </c>
       <c r="W27" t="n">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="X27" t="n">
-        <v>35.4</v>
+        <v>35.1</v>
       </c>
       <c r="Y27" t="n">
         <v>17</v>
@@ -6943,10 +6943,10 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>0.544</v>
+        <v>0.543</v>
       </c>
       <c r="W28" t="n">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="X28" t="n">
         <v>16.1</v>
@@ -7178,10 +7178,10 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W29" t="n">
-        <v>55053</v>
+        <v>55269</v>
       </c>
       <c r="X29" t="n">
-        <v>46.6</v>
+        <v>46.8</v>
       </c>
       <c r="Y29" t="n">
         <v>5</v>
@@ -7637,13 +7637,13 @@
         </is>
       </c>
       <c r="V31" t="n">
-        <v>0.145</v>
+        <v>0.146</v>
       </c>
       <c r="W31" t="n">
-        <v>1460</v>
+        <v>1447</v>
       </c>
       <c r="X31" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="Y31" t="n">
         <v>152</v>
@@ -7869,13 +7869,13 @@
         </is>
       </c>
       <c r="V32" t="n">
-        <v>0.09</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="W32" t="n">
-        <v>637</v>
+        <v>646</v>
       </c>
       <c r="X32" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="Y32" t="n">
         <v>-5</v>
@@ -8339,7 +8339,7 @@
         <v>175</v>
       </c>
       <c r="X34" t="n">
-        <v>5.14</v>
+        <v>5.11</v>
       </c>
       <c r="Y34" t="n">
         <v>31</v>
@@ -8564,7 +8564,7 @@
         <v>1.135</v>
       </c>
       <c r="W35" t="n">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="X35" t="n">
         <v>261</v>
@@ -8793,13 +8793,13 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>0.174</v>
+        <v>0.173</v>
       </c>
       <c r="W36" t="n">
-        <v>3685</v>
+        <v>3692</v>
       </c>
       <c r="X36" t="n">
-        <v>6.95</v>
+        <v>6.96</v>
       </c>
       <c r="Y36" t="n">
         <v>2</v>
@@ -9028,7 +9028,7 @@
         <v>0.01</v>
       </c>
       <c r="W37" t="n">
-        <v>15241</v>
+        <v>15253</v>
       </c>
       <c r="X37" t="n">
         <v>14</v>
@@ -9259,7 +9259,7 @@
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="n">
-        <v>6.26</v>
+        <v>6.25</v>
       </c>
       <c r="Y38" t="n">
         <v>-68</v>
@@ -9485,13 +9485,13 @@
         </is>
       </c>
       <c r="V39" t="n">
-        <v>0.066</v>
+        <v>0.067</v>
       </c>
       <c r="W39" t="n">
-        <v>1691</v>
+        <v>1675</v>
       </c>
       <c r="X39" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="Y39" t="n">
         <v>-87</v>
@@ -9720,7 +9720,7 @@
         <v>0.004</v>
       </c>
       <c r="W40" t="n">
-        <v>44447</v>
+        <v>44409</v>
       </c>
       <c r="X40" t="n">
         <v>329</v>
@@ -9949,13 +9949,13 @@
         </is>
       </c>
       <c r="V41" t="n">
-        <v>0.374</v>
+        <v>0.379</v>
       </c>
       <c r="W41" t="n">
-        <v>1052</v>
+        <v>1038</v>
       </c>
       <c r="X41" t="n">
-        <v>53.6</v>
+        <v>52.9</v>
       </c>
       <c r="Y41" t="n">
         <v>21</v>
@@ -10184,10 +10184,10 @@
         <v>0.124</v>
       </c>
       <c r="W42" t="n">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="X42" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="Y42" t="n">
         <v>-1</v>
@@ -10413,13 +10413,13 @@
         </is>
       </c>
       <c r="V43" t="n">
-        <v>1.662</v>
+        <v>1.711</v>
       </c>
       <c r="W43" t="n">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="X43" t="n">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="Y43" t="n">
         <v>-14</v>
@@ -10645,13 +10645,13 @@
         </is>
       </c>
       <c r="V44" t="n">
-        <v>0.532</v>
+        <v>0.528</v>
       </c>
       <c r="W44" t="n">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="X44" t="n">
-        <v>34.8</v>
+        <v>35.1</v>
       </c>
       <c r="Y44" t="n">
         <v>21</v>
@@ -10880,10 +10880,10 @@
         <v>0.045</v>
       </c>
       <c r="W45" t="n">
-        <v>5231</v>
+        <v>5217</v>
       </c>
       <c r="X45" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="Y45" t="n">
         <v>13</v>
@@ -11109,13 +11109,13 @@
         </is>
       </c>
       <c r="V46" t="n">
-        <v>0.339</v>
+        <v>0.328</v>
       </c>
       <c r="W46" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="X46" t="n">
-        <v>22.7</v>
+        <v>23.4</v>
       </c>
       <c r="Y46" t="n">
         <v>12</v>
@@ -11341,10 +11341,10 @@
         </is>
       </c>
       <c r="V47" t="n">
-        <v>4.42</v>
+        <v>4.455</v>
       </c>
       <c r="W47" t="n">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="n">
@@ -11574,10 +11574,10 @@
         <v>0.043</v>
       </c>
       <c r="W48" t="n">
-        <v>1594</v>
+        <v>1602</v>
       </c>
       <c r="X48" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="Y48" t="n">
         <v>10</v>
@@ -11803,13 +11803,13 @@
         </is>
       </c>
       <c r="V49" t="n">
-        <v>0.502</v>
+        <v>0.504</v>
       </c>
       <c r="W49" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="X49" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="Y49" t="n">
         <v>-44</v>
@@ -12273,7 +12273,7 @@
         <v>363</v>
       </c>
       <c r="X51" t="n">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="Y51" t="n">
         <v>-61</v>
@@ -12721,13 +12721,13 @@
         </is>
       </c>
       <c r="V53" t="n">
-        <v>0.363</v>
+        <v>0.362</v>
       </c>
       <c r="W53" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="X53" t="n">
-        <v>95.5</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="Y53" t="n">
         <v>246</v>
@@ -12953,13 +12953,13 @@
         </is>
       </c>
       <c r="V54" t="n">
-        <v>0.239</v>
+        <v>0.24</v>
       </c>
       <c r="W54" t="n">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="X54" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="Y54" t="n">
         <v>16</v>
@@ -13413,13 +13413,13 @@
         </is>
       </c>
       <c r="V56" t="n">
-        <v>0.843</v>
+        <v>0.841</v>
       </c>
       <c r="W56" t="n">
-        <v>3750</v>
+        <v>3757</v>
       </c>
       <c r="X56" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="Y56" t="n">
         <v>2</v>
@@ -13648,10 +13648,10 @@
         <v>0.23</v>
       </c>
       <c r="W57" t="n">
-        <v>1733</v>
+        <v>1735</v>
       </c>
       <c r="X57" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="Y57" t="n">
         <v>-3</v>
@@ -13877,13 +13877,13 @@
         </is>
       </c>
       <c r="V58" t="n">
-        <v>0.247</v>
+        <v>0.249</v>
       </c>
       <c r="W58" t="n">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="X58" t="n">
-        <v>52.8</v>
+        <v>52.6</v>
       </c>
       <c r="Y58" t="n">
         <v>-4</v>
@@ -14341,13 +14341,13 @@
         </is>
       </c>
       <c r="V60" t="n">
-        <v>0.475</v>
+        <v>0.479</v>
       </c>
       <c r="W60" t="n">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="X60" t="n">
-        <v>42.2</v>
+        <v>41.9</v>
       </c>
       <c r="Y60" t="n">
         <v>6</v>
@@ -14573,13 +14573,13 @@
         </is>
       </c>
       <c r="V61" t="n">
-        <v>0.269</v>
+        <v>0.266</v>
       </c>
       <c r="W61" t="n">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="X61" t="n">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Y61" t="n">
         <v>-66</v>
@@ -14808,10 +14808,10 @@
         <v>0.041</v>
       </c>
       <c r="W62" t="n">
-        <v>3306</v>
+        <v>3286</v>
       </c>
       <c r="X62" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="Y62" t="n">
         <v>-4</v>
@@ -15269,13 +15269,13 @@
         </is>
       </c>
       <c r="V64" t="n">
-        <v>0.103</v>
+        <v>0.105</v>
       </c>
       <c r="W64" t="n">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="X64" t="n">
-        <v>7.78</v>
+        <v>7.65</v>
       </c>
       <c r="Y64" t="n">
         <v>118</v>
@@ -15732,7 +15732,7 @@
         <v>0.012</v>
       </c>
       <c r="W66" t="n">
-        <v>3815</v>
+        <v>3837</v>
       </c>
       <c r="X66" t="inlineStr"/>
       <c r="Y66" t="n">
@@ -15962,7 +15962,7 @@
         <v>0.074</v>
       </c>
       <c r="W67" t="n">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="X67" t="n">
         <v>13.5</v>
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -16136,7 +16136,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F68" t="n">
         <v>8</v>
@@ -16191,13 +16191,13 @@
         </is>
       </c>
       <c r="V68" t="n">
-        <v>0.099</v>
+        <v>0.1</v>
       </c>
       <c r="W68" t="n">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="X68" t="n">
-        <v>27.8</v>
+        <v>27.4</v>
       </c>
       <c r="Y68" t="n">
         <v>24</v>
@@ -16426,7 +16426,7 @@
         <v>0.033</v>
       </c>
       <c r="W69" t="n">
-        <v>1467</v>
+        <v>1471</v>
       </c>
       <c r="X69" t="n">
         <v>25.7</v>
@@ -16658,10 +16658,10 @@
         <v>0</v>
       </c>
       <c r="W70" t="n">
-        <v>4891</v>
+        <v>4897</v>
       </c>
       <c r="X70" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="Y70" t="n">
         <v>26</v>
@@ -16890,10 +16890,10 @@
         <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>3465</v>
+        <v>3448</v>
       </c>
       <c r="X71" t="n">
-        <v>45.1</v>
+        <v>44.9</v>
       </c>
       <c r="Y71" t="n">
         <v>5</v>
@@ -17122,7 +17122,7 @@
         <v>0.003</v>
       </c>
       <c r="W72" t="n">
-        <v>12696</v>
+        <v>12690</v>
       </c>
       <c r="X72" t="n">
         <v>40.5</v>
@@ -17354,10 +17354,10 @@
         <v>0.03</v>
       </c>
       <c r="W73" t="n">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="X73" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="Y73" t="n">
         <v>27</v>
@@ -17586,7 +17586,7 @@
         <v>0.052</v>
       </c>
       <c r="W74" t="n">
-        <v>948</v>
+        <v>955</v>
       </c>
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="n">
@@ -17816,10 +17816,10 @@
         <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>3830</v>
+        <v>3840</v>
       </c>
       <c r="X75" t="n">
-        <v>86.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="Y75" t="n">
         <v>42</v>
@@ -18048,10 +18048,10 @@
         <v>0.006</v>
       </c>
       <c r="W76" t="n">
-        <v>4858</v>
+        <v>4812</v>
       </c>
       <c r="X76" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="Y76" t="n">
         <v>23</v>
@@ -18276,10 +18276,10 @@
         <v>0</v>
       </c>
       <c r="W77" t="n">
-        <v>31276</v>
+        <v>31561</v>
       </c>
       <c r="X77" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Y77" t="n">
         <v>62</v>
@@ -18508,10 +18508,10 @@
         <v>0</v>
       </c>
       <c r="W78" t="n">
-        <v>106130</v>
+        <v>106620</v>
       </c>
       <c r="X78" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="Y78" t="n">
         <v>18</v>
@@ -18737,10 +18737,10 @@
         </is>
       </c>
       <c r="V79" t="n">
-        <v>0.363</v>
+        <v>0.36</v>
       </c>
       <c r="W79" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="n">
@@ -18967,10 +18967,10 @@
         </is>
       </c>
       <c r="V80" t="n">
-        <v>0.242</v>
+        <v>0.241</v>
       </c>
       <c r="W80" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="X80" t="n">
         <v>22.1</v>
@@ -19202,10 +19202,10 @@
         <v>0.025</v>
       </c>
       <c r="W81" t="n">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="X81" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="n">

--- a/output/2026-10-16/enriched_analysis.xlsx
+++ b/output/2026-10-16/enriched_analysis.xlsx
@@ -12953,37 +12953,37 @@
         </is>
       </c>
       <c r="V54" t="n">
-        <v>0.24</v>
+        <v>0.241</v>
       </c>
       <c r="W54" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="X54" t="n">
-        <v>14.2</v>
+        <v>16.6</v>
       </c>
       <c r="Y54" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.79</v>
+        <v>6.88</v>
       </c>
       <c r="AA54" t="n">
-        <v>-30</v>
+        <v>-43</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.21</v>
+        <v>0.55</v>
       </c>
       <c r="AC54" t="n">
         <v>18</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.83</v>
+        <v>3.06</v>
       </c>
       <c r="AG54" t="n">
         <v>27.05</v>
